--- a/casos_saucedemo.xlsx
+++ b/casos_saucedemo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\caso_teste_saucedemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1EE5D4-7DAC-46EB-A7D4-6AD7F6047901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDBA2AE3-3143-4743-B932-2EA7CDA8E6FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10260" yWindow="2160" windowWidth="10230" windowHeight="8640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Saucedemo" sheetId="1" r:id="rId1"/>
@@ -220,9 +220,6 @@
     <t>Produto: Sauce Labs Backpack</t>
   </si>
   <si>
-    <t>Sistema não deve duplicar item e botão deve mudar para “Remove”</t>
-  </si>
-  <si>
     <t>TC007</t>
   </si>
   <si>
@@ -339,10 +336,6 @@
 carrinho e impedir acesso ao checkout.</t>
   </si>
   <si>
-    <t>Sistema exibiu mensagem de
-usuário/senha inválidos.</t>
-  </si>
-  <si>
     <t>Sistema deve autenticar o usuário e redirecionar para "/inventory.html"</t>
   </si>
   <si>
@@ -361,8 +354,14 @@
   <si>
     <t>1. Navegar até a página de produtos
 2. Selecionar um produto "Sauce Labs Backpack"
-3. Clicar em 'Add to Cart' 2 vezes
+3. Clicar em 'Add to Cart'
 4. Verificar o carrinho</t>
+  </si>
+  <si>
+    <t>Sistema não deve permitir adicionais mais de "1" item e botão deve mudar para “Remove”</t>
+  </si>
+  <si>
+    <t>Sistema exibiu mensagem de erro "Epic sadface: Username and password do not match any user in this service".</t>
   </si>
 </sst>
 </file>
@@ -999,7 +998,7 @@
         <v>36</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J2" s="17" t="s">
         <v>20</v>
@@ -1014,13 +1013,13 @@
         <v>23</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O2" s="8" t="s">
         <v>54</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q2" s="8" t="s">
         <v>42</v>
@@ -1058,7 +1057,7 @@
         <v>37</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J3" s="17" t="s">
         <v>20</v>
@@ -1073,13 +1072,13 @@
         <v>38</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O3" s="8" t="s">
         <v>54</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q3" s="8" t="s">
         <v>42</v>
@@ -1111,13 +1110,13 @@
         <v>47</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J4" s="17" t="s">
         <v>20</v>
@@ -1132,13 +1131,13 @@
         <v>39</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O4" s="8" t="s">
         <v>54</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q4" s="8" t="s">
         <v>42</v>
@@ -1170,13 +1169,13 @@
         <v>33</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>60</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="J5" s="15" t="s">
         <v>58</v>
@@ -1187,17 +1186,17 @@
       <c r="L5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="M5" s="21" t="s">
-        <v>91</v>
+      <c r="M5" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O5" s="8" t="s">
         <v>54</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q5" s="8" t="s">
         <v>42</v>
@@ -1223,10 +1222,10 @@
         <v>52</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>55</v>
@@ -1247,16 +1246,16 @@
         <v>22</v>
       </c>
       <c r="M6" s="21" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="N6" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O6" s="8" t="s">
         <v>54</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q6" s="8" t="s">
         <v>42</v>
@@ -1276,25 +1275,25 @@
         <v>51</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="8" t="s">
+      <c r="F7" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H7" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>66</v>
-      </c>
       <c r="I7" s="21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J7" s="16" t="s">
         <v>20</v>
@@ -1306,16 +1305,16 @@
         <v>27</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O7" s="8" t="s">
         <v>54</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q7" s="8" t="s">
         <v>42</v>
@@ -1332,28 +1331,28 @@
     </row>
     <row r="8" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C8" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" s="10" t="s">
+      <c r="F8" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>70</v>
-      </c>
       <c r="G8" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J8" s="15" t="s">
         <v>58</v>
@@ -1365,16 +1364,16 @@
         <v>22</v>
       </c>
       <c r="M8" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O8" s="8" t="s">
         <v>54</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q8" s="8" t="s">
         <v>42</v>
@@ -1391,26 +1390,26 @@
     </row>
     <row r="9" spans="2:20" ht="30" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C9" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9" s="8" t="s">
+      <c r="F9" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>74</v>
-      </c>
       <c r="G9" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J9" s="15" t="s">
         <v>58</v>
@@ -1422,16 +1421,16 @@
         <v>22</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O9" s="8" t="s">
         <v>54</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q9" s="8" t="s">
         <v>42</v>
